--- a/contribution document.xlsx
+++ b/contribution document.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveabertayac-my.sharepoint.com/personal/2601298_uad_ac_uk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2600854\Documents\Clarity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE0C49F7-D155-40D0-9926-CD89DEEE1015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F890E0-F4C3-44B3-8CE0-98CF17D5E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>Task</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>player input</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -337,37 +340,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color theme="0"/>
@@ -591,14 +564,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D52FD46C-2427-4749-937B-6AE10369247D}" name="Task Weight" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Progress" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Dominic Nelson" dataDxfId="7" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hector Bisset" dataDxfId="6" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{D52FD46C-2427-4749-937B-6AE10369247D}" name="Task Weight" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Progress" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Dominic Nelson" dataDxfId="4" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hector Bisset" dataDxfId="3" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1048,10 +1021,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1440,13 +1413,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C22">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$C2="To start"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$C2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$C2="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
